--- a/files/港岛-寿臣山及浅水湾-No.3 Repulse Bay Road.xlsx
+++ b/files/港岛-寿臣山及浅水湾-No.3 Repulse Bay Road.xlsx
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>3250</v>
+        <v>3316</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>3510</v>
+        <v>3574</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>1632</v>
+        <v>1659</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>28300300</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>17341</v>
+        <v>17059</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1709</v>
+        <v>1740</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         <v>51570000</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>30176</v>
+        <v>29638</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1632</v>
+        <v>1659</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>56540000</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>34645</v>
+        <v>34081</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1709</v>
+        <v>1740</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>51930000</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>30386</v>
+        <v>29845</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1682</v>
+        <v>1715</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>49872000</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>29650</v>
+        <v>29080</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1741</v>
+        <v>1770</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>57500000</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>33027</v>
+        <v>32486</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1682</v>
+        <v>1715</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>49872000</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>29650</v>
+        <v>29080</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1741</v>
+        <v>1770</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>51681600</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>29685</v>
+        <v>29199</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1682</v>
+        <v>1715</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1741</v>
+        <v>1770</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1682</v>
+        <v>1715</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1741</v>
+        <v>1770</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>58545000</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>33627</v>
+        <v>33076</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1671</v>
+        <v>1715</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1741</v>
+        <v>1770</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>23592042</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>13551</v>
+        <v>13329</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1671</v>
+        <v>1715</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1741</v>
+        <v>1770</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1671</v>
+        <v>1715</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>52000000</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>31119</v>
+        <v>30321</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1741</v>
+        <v>1770</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1671</v>
+        <v>1715</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>47000000</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>28127</v>
+        <v>27405</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1741</v>
+        <v>1770</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>51800000</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>29753</v>
+        <v>29266</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1671</v>
+        <v>1715</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>54000000</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>32316</v>
+        <v>31487</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1741</v>
+        <v>1770</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>52000000</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>29868</v>
+        <v>29379</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1671</v>
+        <v>1715</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>46700000</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>27947</v>
+        <v>27230</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1796</v>
+        <v>1770</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>48000000</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>26726</v>
+        <v>27119</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1664</v>
+        <v>1715</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1734</v>
+        <v>1771</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>48000000</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>27682</v>
+        <v>27103</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1664</v>
+        <v>1715</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>50200000</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>30168</v>
+        <v>29271</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1734</v>
+        <v>1771</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>47800000</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>27566</v>
+        <v>26990</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1664</v>
+        <v>1715</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>50000000</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>30048</v>
+        <v>29155</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1734</v>
+        <v>1771</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>53310000</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>30744</v>
+        <v>30102</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>1664</v>
+        <v>1715</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>48500000</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>29147</v>
+        <v>28280</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>1734</v>
+        <v>1771</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>47600000</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>27451</v>
+        <v>26877</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>1659</v>
+        <v>1715</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>47500000</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>28632</v>
+        <v>27697</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>1734</v>
+        <v>1771</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>47600000</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>27451</v>
+        <v>26877</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>1659</v>
+        <v>1715</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>47500000</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>28632</v>
+        <v>27697</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>1734</v>
+        <v>1771</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>48600000</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>28028</v>
+        <v>27442</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>1659</v>
+        <v>1715</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>47000000</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>28330</v>
+        <v>27405</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>1734</v>
+        <v>1771</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>1659</v>
+        <v>1715</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>47200000</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>28451</v>
+        <v>27522</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>1734</v>
+        <v>1771</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>A | 3510呎 (4+房)
+          <t>A | 3574呎 (4+房)
 -
 -
 (待售)</t>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
-          <t>B | 3250呎 (4+房)
+          <t>B | 3316呎 (4+房)
 -
 -
 (待售)</t>
@@ -3685,17 +3685,17 @@
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>A | 1709呎 (4+房)
+          <t>A | 1740呎 (4+房)
 $5157万
-$30,176/呎
+$29,638/呎
 (97年-06月-27日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>B | 1632呎 (4+房)
+          <t>B | 1659呎 (4+房)
 $2830万
-$17,341/呎
+$17,059/呎
 (99年-06月-11日)</t>
         </is>
       </c>
@@ -3708,17 +3708,17 @@
       </c>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t>A | 1709呎 (4+房)
+          <t>A | 1740呎 (4+房)
 $5193万
-$30,386/呎
+$29,845/呎
 (97年-06月-27日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
         <is>
-          <t>B | 1632呎 (4+房)
+          <t>B | 1659呎 (4+房)
 $5654万
-$34,645/呎
+$34,081/呎
 (97年-07月-08日)</t>
         </is>
       </c>
@@ -3731,17 +3731,17 @@
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>A | 1741呎 (4+房)
+          <t>A | 1770呎 (4+房)
 $5750万
-$33,027/呎
+$32,486/呎
 (97年-07月-08日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>B | 1682呎 (4+房)
+          <t>B | 1715呎 (4+房)
 $4987万
-$29,650/呎
+$29,080/呎
 (97年-12月-16日)</t>
         </is>
       </c>
@@ -3754,17 +3754,17 @@
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>A | 1741呎 (4+房)
+          <t>A | 1770呎 (4+房)
 $5168万
-$29,685/呎
+$29,199/呎
 (97年-07月-19日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
         <is>
-          <t>B | 1682呎 (4+房)
+          <t>B | 1715呎 (4+房)
 $4987万
-$29,650/呎
+$29,080/呎
 (97年-12月-16日)</t>
         </is>
       </c>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>A | 1741呎 (4+房)
+          <t>A | 1770呎 (4+房)
 -
 -
 (待售)</t>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>B | 1682呎 (4+房)
+          <t>B | 1715呎 (4+房)
 -
 -
 (待售)</t>
@@ -3800,15 +3800,15 @@
       </c>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>A | 1741呎 (4+房)
+          <t>A | 1770呎 (4+房)
 $5854万
-$33,627/呎
+$33,076/呎
 (97年-10月-22日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>B | 1682呎 (4+房)
+          <t>B | 1715呎 (4+房)
 -
 -
 (待售)</t>
@@ -3823,15 +3823,15 @@
       </c>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t>A | 1741呎 (4+房)
+          <t>A | 1770呎 (4+房)
 $2359万
-$13,551/呎
+$13,329/呎
 (99年-03月-11日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>B | 1671呎 (4+房)
+          <t>B | 1715呎 (4+房)
 -
 -
 (待售)</t>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>A | 1741呎 (4+房)
+          <t>A | 1770呎 (4+房)
 -
 -
 (待售)</t>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>B | 1671呎 (4+房)
+          <t>B | 1715呎 (4+房)
 -
 -
 (待售)</t>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>A | 1741呎 (4+房)
+          <t>A | 1770呎 (4+房)
 -
 -
 (待售)</t>
@@ -3877,9 +3877,9 @@
       </c>
       <c r="C14" s="21" t="inlineStr">
         <is>
-          <t>B | 1671呎 (4+房)
+          <t>B | 1715呎 (4+房)
 $5200万
-$31,119/呎
+$30,321/呎
 (97年-07月-04日)</t>
         </is>
       </c>
@@ -3892,17 +3892,17 @@
       </c>
       <c r="B15" s="21" t="inlineStr">
         <is>
-          <t>A | 1741呎 (4+房)
+          <t>A | 1770呎 (4+房)
 $5180万
-$29,753/呎
+$29,266/呎
 (97年-06月-25日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
         <is>
-          <t>B | 1671呎 (4+房)
+          <t>B | 1715呎 (4+房)
 $4700万
-$28,127/呎
+$27,405/呎
 (97年-06月-25日)</t>
         </is>
       </c>
@@ -3915,17 +3915,17 @@
       </c>
       <c r="B16" s="21" t="inlineStr">
         <is>
-          <t>A | 1741呎 (4+房)
+          <t>A | 1770呎 (4+房)
 $5200万
-$29,868/呎
+$29,379/呎
 (97年-07月-12日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
         <is>
-          <t>B | 1671呎 (4+房)
+          <t>B | 1715呎 (4+房)
 $5400万
-$32,316/呎
+$31,487/呎
 (97年-07月-12日)</t>
         </is>
       </c>
@@ -3938,17 +3938,17 @@
       </c>
       <c r="B17" s="21" t="inlineStr">
         <is>
-          <t>A | 1796呎 (4+房)
+          <t>A | 1770呎 (4+房)
 $4800万
-$26,726/呎
+$27,119/呎
 (97年-06月-26日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
         <is>
-          <t>B | 1671呎 (4+房)
+          <t>B | 1715呎 (4+房)
 $4670万
-$27,947/呎
+$27,230/呎
 (97年-06月-25日)</t>
         </is>
       </c>
@@ -3961,15 +3961,15 @@
       </c>
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t>A | 1734呎 (4+房)
+          <t>A | 1771呎 (4+房)
 $4800万
-$27,682/呎
+$27,103/呎
 (97年-06月-27日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>B | 1664呎 (4+房)
+          <t>B | 1715呎 (4+房)
 -
 -
 (待售)</t>
@@ -3984,17 +3984,17 @@
       </c>
       <c r="B19" s="21" t="inlineStr">
         <is>
-          <t>A | 1734呎 (4+房)
+          <t>A | 1771呎 (4+房)
 $4780万
-$27,566/呎
+$26,990/呎
 (97年-07月-04日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
         <is>
-          <t>B | 1664呎 (4+房)
+          <t>B | 1715呎 (4+房)
 $5020万
-$30,168/呎
+$29,271/呎
 (97年-07月-08日)</t>
         </is>
       </c>
@@ -4007,17 +4007,17 @@
       </c>
       <c r="B20" s="21" t="inlineStr">
         <is>
-          <t>A | 1734呎 (4+房)
+          <t>A | 1771呎 (4+房)
 $5331万
-$30,744/呎
+$30,102/呎
 (97年-07月-07日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>B | 1664呎 (4+房)
+          <t>B | 1715呎 (4+房)
 $5000万
-$30,048/呎
+$29,155/呎
 (97年-07月-07日)</t>
         </is>
       </c>
@@ -4030,17 +4030,17 @@
       </c>
       <c r="B21" s="21" t="inlineStr">
         <is>
-          <t>A | 1734呎 (4+房)
+          <t>A | 1771呎 (4+房)
 $4760万
-$27,451/呎
+$26,877/呎
 (97年-06月-27日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
         <is>
-          <t>B | 1664呎 (4+房)
+          <t>B | 1715呎 (4+房)
 $4850万
-$29,147/呎
+$28,280/呎
 (97年-07月-11日)</t>
         </is>
       </c>
@@ -4053,17 +4053,17 @@
       </c>
       <c r="B22" s="21" t="inlineStr">
         <is>
-          <t>A | 1734呎 (4+房)
+          <t>A | 1771呎 (4+房)
 $4760万
-$27,451/呎
+$26,877/呎
 (97年-06月-27日)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>B | 1659呎 (4+房)
+          <t>B | 1715呎 (4+房)
 $4750万
-$28,632/呎
+$27,697/呎
 (97年-07月-17日)</t>
         </is>
       </c>
@@ -4076,17 +4076,17 @@
       </c>
       <c r="B23" s="21" t="inlineStr">
         <is>
-          <t>A | 1734呎 (4+房)
+          <t>A | 1771呎 (4+房)
 $4860万
-$28,028/呎
+$27,442/呎
 (97年-07月-07日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
         <is>
-          <t>B | 1659呎 (4+房)
+          <t>B | 1715呎 (4+房)
 $4750万
-$28,632/呎
+$27,697/呎
 (97年-07月-07日)</t>
         </is>
       </c>
@@ -4099,7 +4099,7 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>A | 1734呎 (4+房)
+          <t>A | 1771呎 (4+房)
 -
 -
 (待售)</t>
@@ -4107,9 +4107,9 @@
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
-          <t>B | 1659呎 (4+房)
+          <t>B | 1715呎 (4+房)
 $4700万
-$28,330/呎
+$27,405/呎
 (97年-07月-05日)</t>
         </is>
       </c>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="B25" s="20" t="inlineStr">
         <is>
-          <t>A | 1734呎 (4+房)
+          <t>A | 1771呎 (4+房)
 -
 -
 (待售)</t>
@@ -4130,9 +4130,9 @@
       </c>
       <c r="C25" s="21" t="inlineStr">
         <is>
-          <t>B | 1659呎 (4+房)
+          <t>B | 1715呎 (4+房)
 $4720万
-$28,451/呎
+$27,522/呎
 (97年-07月-07日)</t>
         </is>
       </c>
